--- a/data/merged/2026-09-09/MERGED_UK_Wet-Dry-Floor-Washer_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_UK_Wet-Dry-Floor-Washer_2026-09-09.xlsx
@@ -6614,50 +6614,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId39" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Product 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId40" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6999,7 +6955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR41"/>
+  <dimension ref="A1:BR40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -15748,40 +15704,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GKHN6VPY</t>
+          <t>B0FZDZCB3J</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>HomeTronix</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0GKHN6VPY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/HomeTronix/page/11959ABE-BE2E-4668-9612-2728130D72BC?lp_asin=B0FZDZCB3J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Karcher Intensive Carpet &amp; Upholstery Cleaner, 1L</t>
+          <t>HomeTronix 30L Wet &amp; Dry Vacuum Cleaner Powerful SuctionsStainless Steel Tank | HEPA Filter | 10M Cable | Quiet ≤80dB | For</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GKHN6VPY?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/414TWaO0hbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/31mxOAo6ZvL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GKHN6VPY</t>
+          <t>B0FZDZCB3J</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -15789,20 +15745,10 @@
           <t>DIY &amp; Tools:Power, Garden &amp; Hand Tools:Power Tools:Wet-Dry Shop Vacuums</t>
         </is>
       </c>
-      <c r="N39" s="14" t="inlineStr">
-        <is>
-          <t>DIY &amp; Tools</t>
-        </is>
-      </c>
-      <c r="O39" s="15">
-        <v>65554</v>
-      </c>
-      <c r="P39" s="15">
-        <v>-63506</v>
-      </c>
-      <c r="Q39" s="16">
-        <v>-0.82</v>
-      </c>
+      <c r="N39" s="14"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="16"/>
       <c r="R39" s="17" t="inlineStr">
         <is>
           <t>Wet-Dry Shop Vacuums</t>
@@ -15810,48 +15756,46 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="T39" s="15">
-        <v>26</v>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="T39" s="15"/>
       <c r="U39" s="16"/>
-      <c r="V39" s="15">
-        <v>286</v>
-      </c>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X39" s="15">
+        <v>2750</v>
+      </c>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>10.99</v>
+        <v>54.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
-      <c r="AD39" s="19"/>
+      <c r="AD39" s="19">
+        <v>26</v>
+      </c>
       <c r="AE39" s="15"/>
-      <c r="AF39" s="21"/>
+      <c r="AF39" s="21">
+        <v>3.6</v>
+      </c>
       <c r="AG39" s="22">
         <v>0</v>
       </c>
-      <c r="AH39" s="20">
-        <v>3.1</v>
-      </c>
+      <c r="AH39" s="20"/>
       <c r="AI39" s="16">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="AJ39"/>
-      <c r="AK39" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="AL39" s="19">
-        <v>86</v>
-      </c>
+      <c r="AK39" s="13"/>
+      <c r="AL39" s="19"/>
       <c r="AM39" s="13" t="inlineStr">
         <is>
           <t>FBM</t>
@@ -15862,11 +15806,11 @@
       <c r="AP39"/>
       <c r="AQ39" s="19"/>
       <c r="AR39" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Official UK</t>
+          <t>Allied UK</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
@@ -15874,19 +15818,11 @@
           <t>FBM</t>
         </is>
       </c>
-      <c r="AU39" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV39" s="14" t="inlineStr">
-        <is>
-          <t>BANBURY Oxfordshire OX16 3ED GB</t>
-        </is>
-      </c>
+      <c r="AU39" s="13"/>
+      <c r="AV39" s="14"/>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25JEMXHVTW348</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15X7NQ5D2ODTD</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
@@ -15894,8 +15830,16 @@
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
-      <c r="BC39" s="13"/>
-      <c r="BD39" s="13"/>
+      <c r="BC39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="13"/>
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
@@ -15903,49 +15847,25 @@
       <c r="BI39" s="23"/>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>1.2 kg</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>1.20 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>21.5 x 10 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>21.50 x 10.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BN39" s="23" t="inlineStr">
-        <is>
-          <t>1.15 kg</t>
-        </is>
-      </c>
-      <c r="BO39" s="23" t="inlineStr">
-        <is>
-          <t>1.15 kg</t>
-        </is>
-      </c>
-      <c r="BP39" s="23" t="inlineStr">
-        <is>
-          <t>21.5 x 10 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BQ39" s="23" t="inlineStr">
-        <is>
-          <t>21.50 x 10.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BR39" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
+          <t>30L x 30W x 60H centimetres</t>
+        </is>
+      </c>
+      <c r="BM39" s="23"/>
+      <c r="BN39" s="23"/>
+      <c r="BO39" s="23"/>
+      <c r="BP39" s="23"/>
+      <c r="BQ39" s="23"/>
+      <c r="BR39" s="13"/>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
@@ -15954,40 +15874,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0FZDZCB3J</t>
+          <t>B0HC6QW1ZS</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>HomeTronix</t>
+          <t>hetch</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/HomeTronix/page/11959ABE-BE2E-4668-9612-2728130D72BC?lp_asin=B0FZDZCB3J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=hetch</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>HomeTronix 30L Wet &amp; Dry Vacuum Cleaner Powerful SuctionsStainless Steel Tank | HEPA Filter | 10M Cable | Quiet ≤80dB | For</t>
+          <t>HETCH V10 800W Wet &amp; Dry Vacuum, Carpet Cleaner &amp; Stain Remover 14Ls3-in-1 wet extractor &amp; blower for upholstery, rugs, sta</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HC6QW1ZS?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/31mxOAo6ZvL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/417yFSyZqvL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0FZDZCB3J</t>
+          <t>B0HC6QW1ZS</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -15999,43 +15919,27 @@
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="16"/>
-      <c r="R40" s="17" t="inlineStr">
-        <is>
-          <t>Wet-Dry Shop Vacuums</t>
-        </is>
-      </c>
-      <c r="S40" s="18" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="R40" s="17"/>
+      <c r="S40" s="18"/>
       <c r="T40" s="15"/>
       <c r="U40" s="16"/>
       <c r="V40" s="15"/>
-      <c r="W40" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X40" s="15">
-        <v>2750</v>
-      </c>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
       <c r="Y40" s="19">
         <v>1</v>
       </c>
       <c r="Z40" s="20">
-        <v>54.99</v>
+        <v>129.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
-      <c r="AD40" s="19">
-        <v>26</v>
-      </c>
-      <c r="AE40" s="15"/>
-      <c r="AF40" s="21">
-        <v>3.6</v>
-      </c>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="21"/>
       <c r="AG40" s="22">
         <v>0</v>
       </c>
@@ -16048,7 +15952,7 @@
       <c r="AL40" s="19"/>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -16060,19 +15964,19 @@
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Allied UK</t>
+          <t>Hetch UK Official Store</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU40" s="13"/>
       <c r="AV40" s="14"/>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15X7NQ5D2ODTD</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U1ZF1MD2GZLO</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
@@ -16085,11 +15989,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD40" s="13"/>
       <c r="BE40" s="13"/>
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
@@ -16097,171 +15997,21 @@
       <c r="BI40" s="23"/>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>6 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BL40" s="23" t="inlineStr">
-        <is>
-          <t>30L x 30W x 60H centimetres</t>
-        </is>
-      </c>
+          <t>4.00 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="23"/>
       <c r="BM40" s="23"/>
       <c r="BN40" s="23"/>
       <c r="BO40" s="23"/>
       <c r="BP40" s="23"/>
       <c r="BQ40" s="23"/>
       <c r="BR40" s="13"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
-        <v>40</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>B0HC6QW1ZS</t>
-        </is>
-      </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>hetch</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=hetch</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>HETCH V10 800W Wet &amp; Dry Vacuum, Carpet Cleaner &amp; Stain Remover 14Ls3-in-1 wet extractor &amp; blower for upholstery, rugs, sta</t>
-        </is>
-      </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0HC6QW1ZS?psc=1</t>
-        </is>
-      </c>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/417yFSyZqvL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L41" s="14" t="inlineStr">
-        <is>
-          <t>B0HC6QW1ZS</t>
-        </is>
-      </c>
-      <c r="M41" s="14" t="inlineStr">
-        <is>
-          <t>DIY &amp; Tools:Power, Garden &amp; Hand Tools:Power Tools:Wet-Dry Shop Vacuums</t>
-        </is>
-      </c>
-      <c r="N41" s="14"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="20">
-        <v>129.99</v>
-      </c>
-      <c r="AA41"/>
-      <c r="AB41"/>
-      <c r="AC41" s="2"/>
-      <c r="AD41" s="19"/>
-      <c r="AE41" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="21"/>
-      <c r="AG41" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ41"/>
-      <c r="AK41" s="13"/>
-      <c r="AL41" s="19"/>
-      <c r="AM41" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN41" s="13"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41"/>
-      <c r="AQ41" s="19"/>
-      <c r="AR41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS41" s="14" t="inlineStr">
-        <is>
-          <t>Hetch UK Official Store</t>
-        </is>
-      </c>
-      <c r="AT41" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U1ZF1MD2GZLO</t>
-        </is>
-      </c>
-      <c r="AX41" s="13"/>
-      <c r="AY41" s="13"/>
-      <c r="AZ41" s="13"/>
-      <c r="BA41" s="13"/>
-      <c r="BB41" s="13"/>
-      <c r="BC41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD41" s="13"/>
-      <c r="BE41" s="13"/>
-      <c r="BF41" s="13"/>
-      <c r="BG41" s="13"/>
-      <c r="BH41" s="14"/>
-      <c r="BI41" s="23"/>
-      <c r="BJ41" s="23" t="inlineStr">
-        <is>
-          <t>4 kg</t>
-        </is>
-      </c>
-      <c r="BK41" s="23" t="inlineStr">
-        <is>
-          <t>4.00 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="23"/>
-      <c r="BM41" s="23"/>
-      <c r="BN41" s="23"/>
-      <c r="BO41" s="23"/>
-      <c r="BP41" s="23"/>
-      <c r="BQ41" s="23"/>
-      <c r="BR41" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16546,30 +16296,22 @@
     <hyperlink ref="M38" r:id="rId277" tooltip="https://www.amazon.co.uk/b?node=3576389031"/>
     <hyperlink ref="N38" r:id="rId278"/>
     <hyperlink ref="AW38" r:id="rId279" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SUBASU69VDMX"/>
-    <hyperlink ref="C39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0GKHN6VPY"/>
-    <hyperlink ref="G39" r:id="rId281" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0GKHN6VPY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId282" tooltip="https://www.amazon.co.uk/dp/B0GKHN6VPY?psc=1"/>
-    <hyperlink ref="K39" r:id="rId283" tooltip="https://m.media-amazon.com/images/I/414TWaO0hbL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0GKHN6VPY"/>
+    <hyperlink ref="C39" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
+    <hyperlink ref="G39" r:id="rId281" tooltip="https://www.amazon.co.uk/stores/HomeTronix/page/11959ABE-BE2E-4668-9612-2728130D72BC?lp_asin=B0FZDZCB3J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J39" r:id="rId282" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1"/>
+    <hyperlink ref="K39" r:id="rId283" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/31mxOAo6ZvL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
     <hyperlink ref="M39" r:id="rId285" tooltip="https://www.amazon.co.uk/b?node=3576389031"/>
-    <hyperlink ref="N39" r:id="rId286"/>
-    <hyperlink ref="AW39" r:id="rId287" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A25JEMXHVTW348"/>
-    <hyperlink ref="C40" r:id="rId288" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
-    <hyperlink ref="G40" r:id="rId289" tooltip="https://www.amazon.co.uk/stores/HomeTronix/page/11959ABE-BE2E-4668-9612-2728130D72BC?lp_asin=B0FZDZCB3J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J40" r:id="rId290" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1"/>
-    <hyperlink ref="K40" r:id="rId291" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/31mxOAo6ZvL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
-    <hyperlink ref="M40" r:id="rId293" tooltip="https://www.amazon.co.uk/b?node=3576389031"/>
-    <hyperlink ref="AW40" r:id="rId294" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15X7NQ5D2ODTD"/>
-    <hyperlink ref="C41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS"/>
-    <hyperlink ref="G41" r:id="rId296" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=hetch"/>
-    <hyperlink ref="J41" r:id="rId297" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS?psc=1"/>
-    <hyperlink ref="K41" r:id="rId298" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/417yFSyZqvL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId299" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS"/>
-    <hyperlink ref="M41" r:id="rId300" tooltip="https://www.amazon.co.uk/b?node=3576389031"/>
-    <hyperlink ref="AW41" r:id="rId301" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U1ZF1MD2GZLO"/>
+    <hyperlink ref="AW39" r:id="rId286" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A15X7NQ5D2ODTD"/>
+    <hyperlink ref="C40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS"/>
+    <hyperlink ref="G40" r:id="rId288" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=hetch"/>
+    <hyperlink ref="J40" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS?psc=1"/>
+    <hyperlink ref="K40" r:id="rId290" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T1/images/I/417yFSyZqvL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0HC6QW1ZS"/>
+    <hyperlink ref="M40" r:id="rId292" tooltip="https://www.amazon.co.uk/b?node=3576389031"/>
+    <hyperlink ref="AW40" r:id="rId293" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U1ZF1MD2GZLO"/>
   </hyperlinks>
-  <drawing r:id="rId302"/>
+  <drawing r:id="rId294"/>
 </worksheet>
 </file>
 
@@ -16639,7 +16381,7 @@
         <v>195.97012578616352</v>
       </c>
       <c r="G2" s="22">
-        <v>0.11471861471861472</v>
+        <v>0.11525915186661834</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16660,7 +16402,7 @@
         <v>241.95454545454547</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06349206349206349</v>
+        <v>0.06379122870605292</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16681,7 +16423,7 @@
         <v>71.88981481481481</v>
       </c>
       <c r="G4" s="22">
-        <v>0.19480519480519481</v>
+        <v>0.19572308807538963</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16702,7 +16444,7 @@
         <v>246.8639705882353</v>
       </c>
       <c r="G5" s="22">
-        <v>0.049062049062049064</v>
+        <v>0.04929322218194998</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16723,7 +16465,7 @@
         <v>127.99050632911393</v>
       </c>
       <c r="G6" s="22">
-        <v>0.056998556998557</v>
+        <v>0.057267125770206595</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16744,7 +16486,7 @@
         <v>274.48148148148147</v>
       </c>
       <c r="G7" s="22">
-        <v>0.01948051948051948</v>
+        <v>0.019572308807538963</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16765,7 +16507,7 @@
         <v>329.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.015873015873015872</v>
+        <v>0.01594780717651323</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16786,7 +16528,7 @@
         <v>235.92156862745097</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0183982683982684</v>
+        <v>0.018484958318231243</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16807,7 +16549,7 @@
         <v>61.19230769230769</v>
       </c>
       <c r="G10" s="22">
-        <v>0.07034632034632035</v>
+        <v>0.07067778180500181</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16828,7 +16570,7 @@
         <v>299.9871794871795</v>
       </c>
       <c r="G11" s="22">
-        <v>0.01406926406926407</v>
+        <v>0.014135556361000362</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16849,7 +16591,7 @@
         <v>113.21195652173913</v>
       </c>
       <c r="G12" s="22">
-        <v>0.03318903318903319</v>
+        <v>0.03334541500543675</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16870,7 +16612,7 @@
         <v>188.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.01875901875901876</v>
+        <v>0.018847408481333816</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16891,7 +16633,7 @@
         <v>50.97352941176471</v>
       </c>
       <c r="G14" s="22">
-        <v>0.06132756132756133</v>
+        <v>0.061616527727437476</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16912,7 +16654,7 @@
         <v>119.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.025613275613275612</v>
+        <v>0.02573396158028271</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16933,7 +16675,7 @@
         <v>105.63888888888889</v>
       </c>
       <c r="G16" s="22">
-        <v>0.025974025974025976</v>
+        <v>0.026096411743385284</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16943,18 +16685,18 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="C17" s="15">
-        <v>11741</v>
+        <v>11455</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="20">
-        <v>111.81904761904762</v>
+        <v>145.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.01893939393939394</v>
+        <v>0.014316781442551649</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16975,7 +16717,7 @@
         <v>46.914027149321264</v>
       </c>
       <c r="G18" s="22">
-        <v>0.039862914862914864</v>
+        <v>0.04005074302283436</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16996,7 +16738,7 @@
         <v>38.98859315589353</v>
       </c>
       <c r="G19" s="22">
-        <v>0.04743867243867244</v>
+        <v>0.0476621964479884</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17017,7 +16759,7 @@
         <v>149.98507462686567</v>
       </c>
       <c r="G20" s="22">
-        <v>0.012085137085137086</v>
+        <v>0.012142080463936208</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17038,7 +16780,7 @@
         <v>99.98765432098766</v>
       </c>
       <c r="G21" s="22">
-        <v>0.01461038961038961</v>
+        <v>0.014679231605654222</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17059,7 +16801,7 @@
         <v>65.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.021284271284271284</v>
+        <v>0.02138455962305183</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17080,7 +16822,7 @@
         <v>89.98701298701299</v>
       </c>
       <c r="G23" s="22">
-        <v>0.013888888888888888</v>
+        <v>0.013954331279449075</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17101,7 +16843,7 @@
         <v>122.40384615384616</v>
       </c>
       <c r="G24" s="22">
-        <v>0.00937950937950938</v>
+        <v>0.009423704240666908</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17122,7 +16864,7 @@
         <v>35.94904458598726</v>
       </c>
       <c r="G25" s="22">
-        <v>0.02831890331890332</v>
+        <v>0.02845233780355201</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17143,7 +16885,7 @@
         <v>150.0</v>
       </c>
       <c r="G26" s="22">
-        <v>0.005411255411255411</v>
+        <v>0.005436752446538601</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17164,7 +16906,7 @@
         <v>97.08108108108108</v>
       </c>
       <c r="G27" s="22">
-        <v>0.006673881673881674</v>
+        <v>0.006705328017397608</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17213,7 +16955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -17277,7 +17019,7 @@
         <v>118.01572327044025</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5735930735930735</v>
+        <v>0.5762957593330917</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17298,7 +17040,7 @@
         <v>241.95454545454547</v>
       </c>
       <c r="G3" s="22">
-        <v>0.06349206349206349</v>
+        <v>0.06379122870605292</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17319,7 +17061,7 @@
         <v>127.99050632911393</v>
       </c>
       <c r="G4" s="22">
-        <v>0.056998556998557</v>
+        <v>0.057267125770206595</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17340,7 +17082,7 @@
         <v>329.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.015873015873015872</v>
+        <v>0.01594780717651323</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17361,7 +17103,7 @@
         <v>235.92156862745097</v>
       </c>
       <c r="G6" s="22">
-        <v>0.0183982683982684</v>
+        <v>0.018484958318231243</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17382,7 +17124,7 @@
         <v>299.9871794871795</v>
       </c>
       <c r="G7" s="22">
-        <v>0.01406926406926407</v>
+        <v>0.014135556361000362</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17403,7 +17145,7 @@
         <v>188.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.01875901875901876</v>
+        <v>0.018847408481333816</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17424,7 +17166,7 @@
         <v>119.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.025613275613275612</v>
+        <v>0.02573396158028271</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17445,7 +17187,7 @@
         <v>109.95138888888889</v>
       </c>
       <c r="G10" s="22">
-        <v>0.025974025974025976</v>
+        <v>0.026096411743385284</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17466,7 +17208,7 @@
         <v>145.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.01424963924963925</v>
+        <v>0.014316781442551649</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17487,7 +17229,7 @@
         <v>114.98958333333333</v>
       </c>
       <c r="G12" s="22">
-        <v>0.017316017316017316</v>
+        <v>0.017397607828923523</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17508,7 +17250,7 @@
         <v>38.98859315589353</v>
       </c>
       <c r="G13" s="22">
-        <v>0.04743867243867244</v>
+        <v>0.0476621964479884</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17529,7 +17271,7 @@
         <v>149.98507462686567</v>
       </c>
       <c r="G14" s="22">
-        <v>0.012085137085137086</v>
+        <v>0.012142080463936208</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17550,7 +17292,7 @@
         <v>99.98765432098766</v>
       </c>
       <c r="G15" s="22">
-        <v>0.01461038961038961</v>
+        <v>0.014679231605654222</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17571,7 +17313,7 @@
         <v>44.452229299363054</v>
       </c>
       <c r="G16" s="22">
-        <v>0.02831890331890332</v>
+        <v>0.02845233780355201</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17592,7 +17334,7 @@
         <v>35.94904458598726</v>
       </c>
       <c r="G17" s="22">
-        <v>0.02831890331890332</v>
+        <v>0.02845233780355201</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17613,7 +17355,7 @@
         <v>97.08108108108108</v>
       </c>
       <c r="G18" s="22">
-        <v>0.006673881673881674</v>
+        <v>0.006705328017397608</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17634,34 +17376,32 @@
         <v>39.986666666666665</v>
       </c>
       <c r="G19" s="22">
-        <v>0.013528138528138528</v>
+        <v>0.013591881116346502</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Official UK</t>
+          <t>Allied UK</t>
         </is>
       </c>
       <c r="B20" s="15">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C20" s="15">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
-      <c r="F20" s="20">
-        <v>11.0</v>
-      </c>
+      <c r="F20" s="20"/>
       <c r="G20" s="22">
-        <v>0.00468975468975469</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Allied UK</t>
+          <t>Hetch UK Official Store</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -17674,25 +17414,6 @@
       <c r="E21" s="15"/>
       <c r="F21" s="20"/>
       <c r="G21" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Hetch UK Official Store</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="22">
         <v>0.0</v>
       </c>
     </row>
